--- a/References/Madhyasth-Darshan/MD-Mapping.xlsx
+++ b/References/Madhyasth-Darshan/MD-Mapping.xlsx
@@ -911,7 +911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2298"/>
+  <dimension ref="A1:K2304"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.4399995803833" defaultRowHeight="15"/>
   <cols>
     <col width="23.21999931335449" customWidth="1" style="114" min="1" max="1"/>
@@ -60825,1433 +60825,1595 @@
       <c r="K2245" s="0" t="n"/>
     </row>
     <row r="2246">
-      <c r="A2246" t="inlineStr">
+      <c r="A2246" s="0" t="inlineStr">
         <is>
           <t>आवर्तनशील अर्थव्यवस्था</t>
         </is>
       </c>
-      <c r="B2246" t="inlineStr">
+      <c r="B2246" s="0" t="inlineStr">
         <is>
           <t>cyclical economy</t>
         </is>
       </c>
-      <c r="C2246" t="inlineStr">
+      <c r="C2246" s="0" t="inlineStr">
         <is>
           <t>avartansheel arthvyavastha</t>
         </is>
       </c>
-      <c r="F2246" t="inlineStr">
+      <c r="F2246" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 1.</t>
         </is>
       </c>
-      <c r="I2246" t="inlineStr">
+      <c r="I2246" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 48</t>
         </is>
       </c>
     </row>
     <row r="2247">
-      <c r="A2247" t="inlineStr">
+      <c r="A2247" s="0" t="inlineStr">
         <is>
           <t>वर्तुलाकार</t>
         </is>
       </c>
-      <c r="B2247" t="inlineStr">
+      <c r="B2247" s="0" t="inlineStr">
         <is>
           <t>circular (shape)</t>
         </is>
       </c>
-      <c r="C2247" t="inlineStr">
+      <c r="C2247" s="0" t="inlineStr">
         <is>
           <t>vartulakar</t>
         </is>
       </c>
-      <c r="F2247" t="inlineStr">
+      <c r="F2247" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 2.</t>
         </is>
       </c>
-      <c r="I2247" t="inlineStr">
+      <c r="I2247" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 25</t>
         </is>
       </c>
     </row>
     <row r="2248">
-      <c r="A2248" t="inlineStr">
+      <c r="A2248" s="0" t="inlineStr">
         <is>
           <t>चक्राकार</t>
         </is>
       </c>
-      <c r="B2248" t="inlineStr">
+      <c r="B2248" s="0" t="inlineStr">
         <is>
           <t>circular (shape)</t>
         </is>
       </c>
-      <c r="C2248" t="inlineStr">
+      <c r="C2248" s="0" t="inlineStr">
         <is>
           <t>chakrakar</t>
         </is>
       </c>
-      <c r="F2248" t="inlineStr">
+      <c r="F2248" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 2.</t>
         </is>
       </c>
-      <c r="I2248" t="inlineStr">
+      <c r="I2248" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 15</t>
         </is>
       </c>
     </row>
     <row r="2249">
-      <c r="A2249" t="inlineStr">
+      <c r="A2249" s="0" t="inlineStr">
         <is>
           <t>तन-मन-धन रूपी अर्थ</t>
         </is>
       </c>
-      <c r="B2249" t="inlineStr">
+      <c r="B2249" s="0" t="inlineStr">
         <is>
           <t>resources in the form of body, mind and wealth</t>
         </is>
       </c>
-      <c r="C2249" t="inlineStr">
+      <c r="C2249" s="0" t="inlineStr">
         <is>
           <t>tan-man-dhan rupi arth</t>
         </is>
       </c>
-      <c r="F2249" t="inlineStr">
+      <c r="F2249" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 3-4.</t>
         </is>
       </c>
-      <c r="I2249" t="inlineStr">
+      <c r="I2249" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 26</t>
         </is>
       </c>
     </row>
     <row r="2250">
-      <c r="A2250" t="inlineStr">
+      <c r="A2250" s="0" t="inlineStr">
         <is>
           <t>धन समृद्धि</t>
         </is>
       </c>
-      <c r="B2250" t="inlineStr">
+      <c r="B2250" s="0" t="inlineStr">
         <is>
           <t>wealthy; being wealthy (noun use)</t>
         </is>
       </c>
-      <c r="C2250" t="inlineStr">
+      <c r="C2250" s="0" t="inlineStr">
         <is>
           <t>dhan samriddhi</t>
         </is>
       </c>
-      <c r="F2250" t="inlineStr">
+      <c r="F2250" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 4.</t>
         </is>
       </c>
-      <c r="I2250" t="inlineStr">
+      <c r="I2250" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 38</t>
         </is>
       </c>
     </row>
     <row r="2251">
-      <c r="A2251" t="inlineStr">
+      <c r="A2251" s="0" t="inlineStr">
         <is>
           <t>श्रम नियोजन स्थली</t>
         </is>
       </c>
-      <c r="B2251" t="inlineStr">
+      <c r="B2251" s="0" t="inlineStr">
         <is>
           <t>sites for the utilisation of labour</t>
         </is>
       </c>
-      <c r="C2251" t="inlineStr">
+      <c r="C2251" s="0" t="inlineStr">
         <is>
           <t>shram niyojan sthali</t>
         </is>
       </c>
-      <c r="F2251" t="inlineStr">
+      <c r="F2251" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 6.</t>
         </is>
       </c>
-      <c r="I2251" t="inlineStr">
+      <c r="I2251" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 26</t>
         </is>
       </c>
     </row>
     <row r="2252">
-      <c r="A2252" t="inlineStr">
+      <c r="A2252" s="0" t="inlineStr">
         <is>
           <t>सदुपयोगिता</t>
         </is>
       </c>
-      <c r="B2252" t="inlineStr">
+      <c r="B2252" s="0" t="inlineStr">
         <is>
           <t>right-use</t>
         </is>
       </c>
-      <c r="C2252" t="inlineStr">
+      <c r="C2252" s="0" t="inlineStr">
         <is>
           <t>sadupyogita</t>
         </is>
       </c>
-      <c r="F2252" t="inlineStr">
+      <c r="F2252" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 8.</t>
         </is>
       </c>
-      <c r="I2252" t="inlineStr">
+      <c r="I2252" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 26</t>
         </is>
       </c>
     </row>
     <row r="2253">
-      <c r="A2253" t="inlineStr">
+      <c r="A2253" s="0" t="inlineStr">
         <is>
           <t>आवश्यकता से अधिक उत्पादन</t>
         </is>
       </c>
-      <c r="B2253" t="inlineStr">
+      <c r="B2253" s="0" t="inlineStr">
         <is>
           <t>production in excess of need</t>
         </is>
       </c>
-      <c r="C2253" t="inlineStr">
+      <c r="C2253" s="0" t="inlineStr">
         <is>
           <t>avashyakta se adhik utpadan</t>
         </is>
       </c>
-      <c r="F2253" t="inlineStr">
+      <c r="F2253" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 10.</t>
         </is>
       </c>
-      <c r="I2253" t="inlineStr">
+      <c r="I2253" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 26</t>
         </is>
       </c>
     </row>
     <row r="2254">
-      <c r="A2254" t="inlineStr">
+      <c r="A2254" s="0" t="inlineStr">
         <is>
           <t>सामान्य आकांक्षा</t>
         </is>
       </c>
-      <c r="B2254" t="inlineStr">
+      <c r="B2254" s="0" t="inlineStr">
         <is>
           <t>common aspirations</t>
         </is>
       </c>
-      <c r="C2254" t="inlineStr">
+      <c r="C2254" s="0" t="inlineStr">
         <is>
           <t>samanya akanksha</t>
         </is>
       </c>
-      <c r="F2254" t="inlineStr">
+      <c r="F2254" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 12.</t>
         </is>
       </c>
-      <c r="I2254" t="inlineStr">
+      <c r="I2254" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 66</t>
         </is>
       </c>
     </row>
     <row r="2255">
-      <c r="A2255" t="inlineStr">
+      <c r="A2255" s="0" t="inlineStr">
         <is>
           <t>परावर्तन विधि</t>
         </is>
       </c>
-      <c r="B2255" t="inlineStr">
+      <c r="B2255" s="0" t="inlineStr">
         <is>
           <t>method of projection</t>
         </is>
       </c>
-      <c r="C2255" t="inlineStr">
+      <c r="C2255" s="0" t="inlineStr">
         <is>
           <t>paravartan vidhi</t>
         </is>
       </c>
-      <c r="F2255" t="inlineStr">
+      <c r="F2255" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 13.</t>
         </is>
       </c>
-      <c r="I2255" t="inlineStr">
+      <c r="I2255" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 26</t>
         </is>
       </c>
     </row>
     <row r="2256">
-      <c r="A2256" t="inlineStr">
+      <c r="A2256" s="0" t="inlineStr">
         <is>
           <t>लाभ</t>
         </is>
       </c>
-      <c r="B2256" t="inlineStr">
+      <c r="B2256" s="0" t="inlineStr">
         <is>
           <t>profit</t>
         </is>
       </c>
-      <c r="C2256" t="inlineStr">
+      <c r="C2256" s="0" t="inlineStr">
         <is>
           <t>labh</t>
         </is>
       </c>
-      <c r="F2256" t="inlineStr">
+      <c r="F2256" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 14.</t>
         </is>
       </c>
-      <c r="I2256" t="inlineStr">
+      <c r="I2256" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 21</t>
         </is>
       </c>
     </row>
     <row r="2257">
-      <c r="A2257" t="inlineStr">
+      <c r="A2257" s="0" t="inlineStr">
         <is>
           <t>लाभ हानि</t>
         </is>
       </c>
-      <c r="B2257" t="inlineStr">
+      <c r="B2257" s="0" t="inlineStr">
         <is>
           <t>profit and loss</t>
         </is>
       </c>
-      <c r="C2257" t="inlineStr">
+      <c r="C2257" s="0" t="inlineStr">
         <is>
           <t>labh hani</t>
         </is>
       </c>
-      <c r="F2257" t="inlineStr">
+      <c r="F2257" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 14.</t>
         </is>
       </c>
-      <c r="I2257" t="inlineStr">
+      <c r="I2257" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 21</t>
         </is>
       </c>
     </row>
     <row r="2258">
-      <c r="A2258" t="inlineStr">
+      <c r="A2258" s="0" t="inlineStr">
         <is>
           <t>लाभोन्मादी अर्थव्यवस्था</t>
         </is>
       </c>
-      <c r="B2258" t="inlineStr">
+      <c r="B2258" s="0" t="inlineStr">
         <is>
           <t>profit-obsessed economy</t>
         </is>
       </c>
-      <c r="C2258" t="inlineStr">
+      <c r="C2258" s="0" t="inlineStr">
         <is>
           <t>labhonmadi arthvyavastha</t>
         </is>
       </c>
-      <c r="F2258" t="inlineStr">
+      <c r="F2258" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 14.</t>
         </is>
       </c>
-      <c r="I2258" t="inlineStr">
+      <c r="I2258" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 48</t>
         </is>
       </c>
     </row>
     <row r="2259">
-      <c r="A2259" t="inlineStr">
+      <c r="A2259" s="0" t="inlineStr">
         <is>
           <t>लाभाकांक्षी</t>
         </is>
       </c>
-      <c r="B2259" t="inlineStr">
+      <c r="B2259" s="0" t="inlineStr">
         <is>
           <t>profit-seeking</t>
         </is>
       </c>
-      <c r="C2259" t="inlineStr">
+      <c r="C2259" s="0" t="inlineStr">
         <is>
           <t>labhakankshi</t>
         </is>
       </c>
-      <c r="F2259" t="inlineStr">
+      <c r="F2259" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 14.</t>
         </is>
       </c>
-      <c r="I2259" t="inlineStr">
+      <c r="I2259" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 46</t>
         </is>
       </c>
     </row>
     <row r="2260">
-      <c r="A2260" t="inlineStr">
+      <c r="A2260" s="0" t="inlineStr">
         <is>
           <t>लाभ प्रथा</t>
         </is>
       </c>
-      <c r="B2260" t="inlineStr">
+      <c r="B2260" s="0" t="inlineStr">
         <is>
           <t>profiteering</t>
         </is>
       </c>
-      <c r="C2260" t="inlineStr">
+      <c r="C2260" s="0" t="inlineStr">
         <is>
           <t>labh pratha</t>
         </is>
       </c>
-      <c r="F2260" t="inlineStr">
+      <c r="F2260" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 14.</t>
         </is>
       </c>
-      <c r="I2260" t="inlineStr">
+      <c r="I2260" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 52</t>
         </is>
       </c>
     </row>
     <row r="2261">
-      <c r="A2261" t="inlineStr">
+      <c r="A2261" s="0" t="inlineStr">
         <is>
           <t>व्यापार</t>
         </is>
       </c>
-      <c r="B2261" t="inlineStr">
+      <c r="B2261" s="0" t="inlineStr">
         <is>
           <t>trade</t>
         </is>
       </c>
-      <c r="C2261" t="inlineStr">
+      <c r="C2261" s="0" t="inlineStr">
         <is>
           <t>vyapar</t>
         </is>
       </c>
-      <c r="F2261" t="inlineStr">
+      <c r="F2261" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 15.</t>
         </is>
       </c>
-      <c r="I2261" t="inlineStr">
+      <c r="I2261" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 7</t>
         </is>
       </c>
     </row>
     <row r="2262">
-      <c r="A2262" t="inlineStr">
+      <c r="A2262" s="0" t="inlineStr">
         <is>
           <t>व्यापार विधि</t>
         </is>
       </c>
-      <c r="B2262" t="inlineStr">
+      <c r="B2262" s="0" t="inlineStr">
         <is>
           <t>the method of trade</t>
         </is>
       </c>
-      <c r="C2262" t="inlineStr">
+      <c r="C2262" s="0" t="inlineStr">
         <is>
           <t>vyapar vidhi</t>
         </is>
       </c>
-      <c r="F2262" t="inlineStr">
+      <c r="F2262" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 15.</t>
         </is>
       </c>
-      <c r="I2262" t="inlineStr">
+      <c r="I2262" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 7</t>
         </is>
       </c>
     </row>
     <row r="2263">
-      <c r="A2263" t="inlineStr">
+      <c r="A2263" s="0" t="inlineStr">
         <is>
           <t>व्यापारोन्मुखी</t>
         </is>
       </c>
-      <c r="B2263" t="inlineStr">
+      <c r="B2263" s="0" t="inlineStr">
         <is>
           <t>trade-oriented</t>
         </is>
       </c>
-      <c r="C2263" t="inlineStr">
+      <c r="C2263" s="0" t="inlineStr">
         <is>
           <t>vyaparonmukhi</t>
         </is>
       </c>
-      <c r="F2263" t="inlineStr">
+      <c r="F2263" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 15.</t>
         </is>
       </c>
-      <c r="I2263" t="inlineStr">
+      <c r="I2263" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 46</t>
         </is>
       </c>
     </row>
     <row r="2264">
-      <c r="A2264" t="inlineStr">
+      <c r="A2264" s="0" t="inlineStr">
         <is>
           <t>पत्र मुद्रा</t>
         </is>
       </c>
-      <c r="B2264" t="inlineStr">
+      <c r="B2264" s="0" t="inlineStr">
         <is>
           <t>paper currency</t>
         </is>
       </c>
-      <c r="C2264" t="inlineStr">
+      <c r="C2264" s="0" t="inlineStr">
         <is>
           <t>patra mudra</t>
         </is>
       </c>
-      <c r="F2264" t="inlineStr">
+      <c r="F2264" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 16.</t>
         </is>
       </c>
-      <c r="I2264" t="inlineStr">
+      <c r="I2264" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 6</t>
         </is>
       </c>
     </row>
     <row r="2265">
-      <c r="A2265" t="inlineStr">
+      <c r="A2265" s="0" t="inlineStr">
         <is>
           <t>धातु मुद्रा</t>
         </is>
       </c>
-      <c r="B2265" t="inlineStr">
+      <c r="B2265" s="0" t="inlineStr">
         <is>
           <t>metal currency</t>
         </is>
       </c>
-      <c r="C2265" t="inlineStr">
+      <c r="C2265" s="0" t="inlineStr">
         <is>
           <t>dhatu mudra</t>
         </is>
       </c>
-      <c r="F2265" t="inlineStr">
+      <c r="F2265" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 16.</t>
         </is>
       </c>
-      <c r="I2265" t="inlineStr">
+      <c r="I2265" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 6</t>
         </is>
       </c>
     </row>
     <row r="2266">
-      <c r="A2266" t="inlineStr">
+      <c r="A2266" s="0" t="inlineStr">
         <is>
           <t>राष्ट्रीय कोष</t>
         </is>
       </c>
-      <c r="B2266" t="inlineStr">
+      <c r="B2266" s="0" t="inlineStr">
+        <is>
+          <t>national reserve(s)</t>
+        </is>
+      </c>
+      <c r="C2266" s="0" t="inlineStr">
+        <is>
+          <t>rashtriya kosh</t>
+        </is>
+      </c>
+      <c r="F2266" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 17.</t>
+        </is>
+      </c>
+      <c r="I2266" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA pp. 44-45, 51</t>
+        </is>
+      </c>
+    </row>
+    <row r="2267">
+      <c r="A2267" s="0" t="inlineStr">
+        <is>
+          <t>सुवर्ण द्रव्य मूलक मूल्यांकन</t>
+        </is>
+      </c>
+      <c r="B2267" s="0" t="inlineStr">
+        <is>
+          <t>gold-based valuation; currency pegged to gold</t>
+        </is>
+      </c>
+      <c r="C2267" s="0" t="inlineStr">
+        <is>
+          <t>suvarna dravya mulak mulyankan</t>
+        </is>
+      </c>
+      <c r="F2267" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 17.</t>
+        </is>
+      </c>
+      <c r="I2267" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 51</t>
+        </is>
+      </c>
+    </row>
+    <row r="2268">
+      <c r="A2268" s="0" t="inlineStr">
+        <is>
+          <t>पूँजी</t>
+        </is>
+      </c>
+      <c r="B2268" s="0" t="inlineStr">
+        <is>
+          <t>capital</t>
+        </is>
+      </c>
+      <c r="C2268" s="0" t="inlineStr">
+        <is>
+          <t>punji</t>
+        </is>
+      </c>
+      <c r="F2268" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 18.</t>
+        </is>
+      </c>
+      <c r="I2268" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 44</t>
+        </is>
+      </c>
+    </row>
+    <row r="2269">
+      <c r="A2269" s="0" t="inlineStr">
+        <is>
+          <t>मूल पूँजी</t>
+        </is>
+      </c>
+      <c r="B2269" s="0" t="inlineStr">
+        <is>
+          <t>primary capital</t>
+        </is>
+      </c>
+      <c r="C2269" s="0" t="inlineStr">
+        <is>
+          <t>mul punji</t>
+        </is>
+      </c>
+      <c r="F2269" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 18.</t>
+        </is>
+      </c>
+      <c r="I2269" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 44</t>
+        </is>
+      </c>
+    </row>
+    <row r="2270">
+      <c r="A2270" s="0" t="inlineStr">
+        <is>
+          <t>ब्याज प्रथा</t>
+        </is>
+      </c>
+      <c r="B2270" s="0" t="inlineStr">
+        <is>
+          <t>practice of collecting interest</t>
+        </is>
+      </c>
+      <c r="C2270" s="0" t="inlineStr">
+        <is>
+          <t>byaj pratha</t>
+        </is>
+      </c>
+      <c r="F2270" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 18.</t>
+        </is>
+      </c>
+      <c r="I2270" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="2271">
+      <c r="A2271" s="0" t="inlineStr">
+        <is>
+          <t>विनिमय</t>
+        </is>
+      </c>
+      <c r="B2271" s="0" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="C2271" s="0" t="inlineStr">
+        <is>
+          <t>vinimay</t>
+        </is>
+      </c>
+      <c r="F2271" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 20.</t>
+        </is>
+      </c>
+      <c r="I2271" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="2272">
+      <c r="A2272" s="0" t="inlineStr">
+        <is>
+          <t>विनिमय प्रणाली</t>
+        </is>
+      </c>
+      <c r="B2272" s="0" t="inlineStr">
+        <is>
+          <t>exchange system</t>
+        </is>
+      </c>
+      <c r="C2272" s="0" t="inlineStr">
+        <is>
+          <t>vinimay pranali</t>
+        </is>
+      </c>
+      <c r="F2272" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 20.</t>
+        </is>
+      </c>
+      <c r="I2272" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 51</t>
+        </is>
+      </c>
+    </row>
+    <row r="2273">
+      <c r="A2273" s="0" t="inlineStr">
+        <is>
+          <t>वस्तु विनिमय प्रणाली</t>
+        </is>
+      </c>
+      <c r="B2273" s="0" t="inlineStr">
+        <is>
+          <t>barter system</t>
+        </is>
+      </c>
+      <c r="C2273" s="0" t="inlineStr">
+        <is>
+          <t>vastu vinimay pranali</t>
+        </is>
+      </c>
+      <c r="F2273" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 20.</t>
+        </is>
+      </c>
+      <c r="I2273" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="2274">
+      <c r="A2274" s="0" t="inlineStr">
+        <is>
+          <t>श्रम विनिमय प्रणाली</t>
+        </is>
+      </c>
+      <c r="B2274" s="0" t="inlineStr">
+        <is>
+          <t>system of exchange of labour</t>
+        </is>
+      </c>
+      <c r="C2274" s="0" t="inlineStr">
+        <is>
+          <t>shram vinimay pranali</t>
+        </is>
+      </c>
+      <c r="F2274" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 20.</t>
+        </is>
+      </c>
+      <c r="I2274" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 62</t>
+        </is>
+      </c>
+    </row>
+    <row r="2275">
+      <c r="A2275" s="0" t="inlineStr">
+        <is>
+          <t>संग्रहण</t>
+        </is>
+      </c>
+      <c r="B2275" s="0" t="inlineStr">
+        <is>
+          <t>accumulating</t>
+        </is>
+      </c>
+      <c r="C2275" s="0" t="inlineStr">
+        <is>
+          <t>sangrahan</t>
+        </is>
+      </c>
+      <c r="F2275" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 21.</t>
+        </is>
+      </c>
+      <c r="I2275" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="2276">
+      <c r="A2276" s="0" t="inlineStr">
+        <is>
+          <t>संग्रहवादी</t>
+        </is>
+      </c>
+      <c r="B2276" s="0" t="inlineStr">
+        <is>
+          <t>accumulation-oriented</t>
+        </is>
+      </c>
+      <c r="C2276" s="0" t="inlineStr">
+        <is>
+          <t>sangrahvadi</t>
+        </is>
+      </c>
+      <c r="F2276" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 21.</t>
+        </is>
+      </c>
+      <c r="I2276" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 46</t>
+        </is>
+      </c>
+    </row>
+    <row r="2277">
+      <c r="A2277" s="0" t="inlineStr">
+        <is>
+          <t>भोगवादी</t>
+        </is>
+      </c>
+      <c r="B2277" s="0" t="inlineStr">
+        <is>
+          <t>indulgence-oriented</t>
+        </is>
+      </c>
+      <c r="C2277" s="0" t="inlineStr">
+        <is>
+          <t>bhogvadi</t>
+        </is>
+      </c>
+      <c r="F2277" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 22.</t>
+        </is>
+      </c>
+      <c r="I2277" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 46</t>
+        </is>
+      </c>
+    </row>
+    <row r="2278">
+      <c r="A2278" s="0" t="inlineStr">
+        <is>
+          <t>उपभोक्तावादी</t>
+        </is>
+      </c>
+      <c r="B2278" s="0" t="inlineStr">
+        <is>
+          <t>consumerist</t>
+        </is>
+      </c>
+      <c r="C2278" s="0" t="inlineStr">
+        <is>
+          <t>upbhoktavadi</t>
+        </is>
+      </c>
+      <c r="F2278" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 22.</t>
+        </is>
+      </c>
+      <c r="I2278" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="2279">
+      <c r="A2279" s="0" t="inlineStr">
+        <is>
+          <t>विलासिता</t>
+        </is>
+      </c>
+      <c r="B2279" s="0" t="inlineStr">
+        <is>
+          <t>luxury</t>
+        </is>
+      </c>
+      <c r="C2279" s="0" t="inlineStr">
+        <is>
+          <t>vilasita</t>
+        </is>
+      </c>
+      <c r="F2279" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 22.</t>
+        </is>
+      </c>
+      <c r="I2279" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" s="0" t="inlineStr">
+        <is>
+          <t>सुविधा संग्रह</t>
+        </is>
+      </c>
+      <c r="B2280" s="0" t="inlineStr">
+        <is>
+          <t>accumulation of comforts</t>
+        </is>
+      </c>
+      <c r="C2280" s="0" t="inlineStr">
+        <is>
+          <t>suvidha sangrah</t>
+        </is>
+      </c>
+      <c r="F2280" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 23.</t>
+        </is>
+      </c>
+      <c r="I2280" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 83</t>
+        </is>
+      </c>
+    </row>
+    <row r="2281">
+      <c r="A2281" s="0" t="inlineStr">
+        <is>
+          <t>सुविधावादी मानसिकता</t>
+        </is>
+      </c>
+      <c r="B2281" s="0" t="inlineStr">
+        <is>
+          <t>comfort-oriented mentality</t>
+        </is>
+      </c>
+      <c r="C2281" s="0" t="inlineStr">
+        <is>
+          <t>suvidhavadi mansikta</t>
+        </is>
+      </c>
+      <c r="F2281" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 23.</t>
+        </is>
+      </c>
+      <c r="I2281" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 75</t>
+        </is>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="A2282" s="0" t="inlineStr">
+        <is>
+          <t>दोहन</t>
+        </is>
+      </c>
+      <c r="B2282" s="0" t="inlineStr">
+        <is>
+          <t>extraction</t>
+        </is>
+      </c>
+      <c r="C2282" s="0" t="inlineStr">
+        <is>
+          <t>dohan</t>
+        </is>
+      </c>
+      <c r="F2282" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 24.</t>
+        </is>
+      </c>
+      <c r="I2282" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 68</t>
+        </is>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" s="0" t="inlineStr">
+        <is>
+          <t>राजगद्दी के कर विधि</t>
+        </is>
+      </c>
+      <c r="B2283" s="0" t="inlineStr">
+        <is>
+          <t>taxation by the throne</t>
+        </is>
+      </c>
+      <c r="C2283" s="0" t="inlineStr">
+        <is>
+          <t>rajgaddi ke kar vidhi</t>
+        </is>
+      </c>
+      <c r="F2283" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 25.</t>
+        </is>
+      </c>
+      <c r="I2283" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="A2284" s="0" t="inlineStr">
+        <is>
+          <t>कर वसूली</t>
+        </is>
+      </c>
+      <c r="B2284" s="0" t="inlineStr">
+        <is>
+          <t>tax collection</t>
+        </is>
+      </c>
+      <c r="C2284" s="0" t="inlineStr">
+        <is>
+          <t>kar vasuli</t>
+        </is>
+      </c>
+      <c r="F2284" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 25.</t>
+        </is>
+      </c>
+      <c r="I2284" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 138</t>
+        </is>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" s="0" t="inlineStr">
+        <is>
+          <t>स्वायत्त</t>
+        </is>
+      </c>
+      <c r="B2285" s="0" t="inlineStr">
+        <is>
+          <t>autonomous</t>
+        </is>
+      </c>
+      <c r="C2285" s="0" t="inlineStr">
+        <is>
+          <t>swayatt</t>
+        </is>
+      </c>
+      <c r="F2285" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 26.</t>
+        </is>
+      </c>
+      <c r="I2285" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="2286">
+      <c r="A2286" s="0" t="inlineStr">
+        <is>
+          <t>स्वावलंबी</t>
+        </is>
+      </c>
+      <c r="B2286" s="0" t="inlineStr">
+        <is>
+          <t>self-reliant</t>
+        </is>
+      </c>
+      <c r="C2286" s="0" t="inlineStr">
+        <is>
+          <t>swavalambi</t>
+        </is>
+      </c>
+      <c r="F2286" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 26.</t>
+        </is>
+      </c>
+      <c r="I2286" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" s="0" t="inlineStr">
+        <is>
+          <t>परिवार मूलक ग्राम स्वराज्य व्यवस्था</t>
+        </is>
+      </c>
+      <c r="B2287" s="0" t="inlineStr">
+        <is>
+          <t>family-based village self-governing system</t>
+        </is>
+      </c>
+      <c r="C2287" s="0" t="inlineStr">
+        <is>
+          <t>parivar mulak gram swarajya vyavastha</t>
+        </is>
+      </c>
+      <c r="F2287" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 27.</t>
+        </is>
+      </c>
+      <c r="I2287" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 110</t>
+        </is>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="A2288" s="0" t="inlineStr">
+        <is>
+          <t>आबंटन</t>
+        </is>
+      </c>
+      <c r="B2288" s="0" t="inlineStr">
+        <is>
+          <t>allotment</t>
+        </is>
+      </c>
+      <c r="C2288" s="0" t="inlineStr">
+        <is>
+          <t>abantan</t>
+        </is>
+      </c>
+      <c r="F2288" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 29.</t>
+        </is>
+      </c>
+      <c r="I2288" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" s="0" t="inlineStr">
+        <is>
+          <t>बंटन</t>
+        </is>
+      </c>
+      <c r="B2289" s="0" t="inlineStr">
+        <is>
+          <t>sharing</t>
+        </is>
+      </c>
+      <c r="C2289" s="0" t="inlineStr">
+        <is>
+          <t>bantan</t>
+        </is>
+      </c>
+      <c r="F2289" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 29.</t>
+        </is>
+      </c>
+      <c r="I2289" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2290">
+      <c r="A2290" s="0" t="inlineStr">
+        <is>
+          <t>वितरण</t>
+        </is>
+      </c>
+      <c r="B2290" s="0" t="inlineStr">
+        <is>
+          <t>distribution</t>
+        </is>
+      </c>
+      <c r="C2290" s="0" t="inlineStr">
+        <is>
+          <t>vitaran</t>
+        </is>
+      </c>
+      <c r="F2290" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 29.</t>
+        </is>
+      </c>
+      <c r="I2290" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="2291">
+      <c r="A2291" s="0" t="inlineStr">
+        <is>
+          <t>कुटीर उद्योग</t>
+        </is>
+      </c>
+      <c r="B2291" s="0" t="inlineStr">
+        <is>
+          <t>cottage industry</t>
+        </is>
+      </c>
+      <c r="C2291" s="0" t="inlineStr">
+        <is>
+          <t>kutir udyog</t>
+        </is>
+      </c>
+      <c r="F2291" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 30.</t>
+        </is>
+      </c>
+      <c r="I2291" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 71</t>
+        </is>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="A2292" s="0" t="inlineStr">
+        <is>
+          <t>ग्राम शिल्प</t>
+        </is>
+      </c>
+      <c r="B2292" s="0" t="inlineStr">
+        <is>
+          <t>village crafts</t>
+        </is>
+      </c>
+      <c r="C2292" s="0" t="inlineStr">
+        <is>
+          <t>gram shilp</t>
+        </is>
+      </c>
+      <c r="F2292" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 30.</t>
+        </is>
+      </c>
+      <c r="I2292" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 71</t>
+        </is>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" s="0" t="inlineStr">
+        <is>
+          <t>ग्रामोद्योग</t>
+        </is>
+      </c>
+      <c r="B2293" s="0" t="inlineStr">
+        <is>
+          <t>village industry</t>
+        </is>
+      </c>
+      <c r="C2293" s="0" t="inlineStr">
+        <is>
+          <t>gramodyog</t>
+        </is>
+      </c>
+      <c r="F2293" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 30.</t>
+        </is>
+      </c>
+      <c r="I2293" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" s="0" t="inlineStr">
+        <is>
+          <t>कृषि</t>
+        </is>
+      </c>
+      <c r="B2294" s="0" t="inlineStr">
+        <is>
+          <t>agriculture</t>
+        </is>
+      </c>
+      <c r="C2294" s="0" t="inlineStr">
+        <is>
+          <t>krishi</t>
+        </is>
+      </c>
+      <c r="F2294" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 30.</t>
+        </is>
+      </c>
+      <c r="I2294" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 71</t>
+        </is>
+      </c>
+    </row>
+    <row r="2295">
+      <c r="A2295" s="0" t="inlineStr">
+        <is>
+          <t>गोपालन</t>
+        </is>
+      </c>
+      <c r="B2295" s="0" t="inlineStr">
+        <is>
+          <t>cattle-rearing</t>
+        </is>
+      </c>
+      <c r="C2295" s="0" t="inlineStr">
+        <is>
+          <t>gopalan</t>
+        </is>
+      </c>
+      <c r="F2295" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 30.</t>
+        </is>
+      </c>
+      <c r="I2295" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 71</t>
+        </is>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="A2296" s="0" t="inlineStr">
+        <is>
+          <t>ठोस</t>
+        </is>
+      </c>
+      <c r="B2296" s="0" t="inlineStr">
+        <is>
+          <t>solid</t>
+        </is>
+      </c>
+      <c r="C2296" s="0" t="inlineStr">
+        <is>
+          <t>thos</t>
+        </is>
+      </c>
+      <c r="F2296" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 35.</t>
+        </is>
+      </c>
+      <c r="I2296" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 34</t>
+        </is>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="A2297" s="0" t="inlineStr">
+        <is>
+          <t>तरल</t>
+        </is>
+      </c>
+      <c r="B2297" s="0" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C2297" s="0" t="inlineStr">
+        <is>
+          <t>taral</t>
+        </is>
+      </c>
+      <c r="F2297" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 35.</t>
+        </is>
+      </c>
+      <c r="I2297" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 34</t>
+        </is>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" s="0" t="inlineStr">
+        <is>
+          <t>विरल वस्तु</t>
+        </is>
+      </c>
+      <c r="B2298" s="0" t="inlineStr">
+        <is>
+          <t>rarefied (gaseous) matter</t>
+        </is>
+      </c>
+      <c r="C2298" s="0" t="inlineStr">
+        <is>
+          <t>viral vastu</t>
+        </is>
+      </c>
+      <c r="F2298" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 35.</t>
+        </is>
+      </c>
+      <c r="I2298" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 34</t>
+        </is>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="A2299" t="inlineStr">
+        <is>
+          <t>राष्ट्रीय मुद्रा कोष, राष्ट्रीय मुद्राकोष</t>
+        </is>
+      </c>
+      <c r="B2299" t="inlineStr">
         <is>
           <t>reserve bank</t>
         </is>
       </c>
-      <c r="C2266" t="inlineStr">
-        <is>
-          <t>rashtriya kosh</t>
-        </is>
-      </c>
-      <c r="F2266" t="inlineStr">
+      <c r="C2299" t="inlineStr">
+        <is>
+          <t>rashtriya mudra kosh</t>
+        </is>
+      </c>
+      <c r="F2299" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 17.</t>
         </is>
       </c>
-      <c r="I2266" t="inlineStr">
+      <c r="I2299" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA pp. 44-45</t>
+        </is>
+      </c>
+    </row>
+    <row r="2300">
+      <c r="A2300" t="inlineStr">
+        <is>
+          <t>अंतर्राष्ट्रीय मुद्रा कोष</t>
+        </is>
+      </c>
+      <c r="B2300" t="inlineStr">
+        <is>
+          <t>International Monetary Fund</t>
+        </is>
+      </c>
+      <c r="C2300" t="inlineStr">
+        <is>
+          <t>antarrashtriya mudra kosh</t>
+        </is>
+      </c>
+      <c r="F2300" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 17.</t>
+        </is>
+      </c>
+      <c r="I2300" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 44</t>
+        </is>
+      </c>
+    </row>
+    <row r="2301">
+      <c r="A2301" t="inlineStr">
+        <is>
+          <t>अन्तर्राष्ट्रीय कोष, अंतर्राष्ट्रीय कोष</t>
+        </is>
+      </c>
+      <c r="B2301" t="inlineStr">
+        <is>
+          <t>international reserves</t>
+        </is>
+      </c>
+      <c r="C2301" t="inlineStr">
+        <is>
+          <t>antarrashtriya kosh</t>
+        </is>
+      </c>
+      <c r="F2301" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 17.</t>
+        </is>
+      </c>
+      <c r="I2301" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 51</t>
         </is>
       </c>
     </row>
-    <row r="2267">
-      <c r="A2267" t="inlineStr">
-        <is>
-          <t>सुवर्ण द्रव्य मूलक मूल्यांकन</t>
-        </is>
-      </c>
-      <c r="B2267" t="inlineStr">
-        <is>
-          <t>gold-based valuation; currency pegged to gold</t>
-        </is>
-      </c>
-      <c r="C2267" t="inlineStr">
-        <is>
-          <t>suvarna dravya mulak mulyankan</t>
-        </is>
-      </c>
-      <c r="F2267" t="inlineStr">
+    <row r="2302">
+      <c r="A2302" t="inlineStr">
+        <is>
+          <t>मुद्रा कोष</t>
+        </is>
+      </c>
+      <c r="B2302" t="inlineStr">
+        <is>
+          <t>currency reserve</t>
+        </is>
+      </c>
+      <c r="C2302" t="inlineStr">
+        <is>
+          <t>mudra kosh</t>
+        </is>
+      </c>
+      <c r="F2302" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 17.</t>
         </is>
       </c>
-      <c r="I2267" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 51</t>
-        </is>
-      </c>
-    </row>
-    <row r="2268">
-      <c r="A2268" t="inlineStr">
-        <is>
-          <t>पूँजी</t>
-        </is>
-      </c>
-      <c r="B2268" t="inlineStr">
-        <is>
-          <t>capital</t>
-        </is>
-      </c>
-      <c r="C2268" t="inlineStr">
-        <is>
-          <t>punji</t>
-        </is>
-      </c>
-      <c r="F2268" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 18.</t>
-        </is>
-      </c>
-      <c r="I2268" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 44</t>
-        </is>
-      </c>
-    </row>
-    <row r="2269">
-      <c r="A2269" t="inlineStr">
-        <is>
-          <t>मूल पूँजी</t>
-        </is>
-      </c>
-      <c r="B2269" t="inlineStr">
-        <is>
-          <t>primary capital</t>
-        </is>
-      </c>
-      <c r="C2269" t="inlineStr">
-        <is>
-          <t>mul punji</t>
-        </is>
-      </c>
-      <c r="F2269" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 18.</t>
-        </is>
-      </c>
-      <c r="I2269" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 44</t>
-        </is>
-      </c>
-    </row>
-    <row r="2270">
-      <c r="A2270" t="inlineStr">
-        <is>
-          <t>ब्याज प्रथा</t>
-        </is>
-      </c>
-      <c r="B2270" t="inlineStr">
-        <is>
-          <t>practice of collecting interest</t>
-        </is>
-      </c>
-      <c r="C2270" t="inlineStr">
-        <is>
-          <t>byaj pratha</t>
-        </is>
-      </c>
-      <c r="F2270" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 18.</t>
-        </is>
-      </c>
-      <c r="I2270" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 52</t>
-        </is>
-      </c>
-    </row>
-    <row r="2271">
-      <c r="A2271" t="inlineStr">
-        <is>
-          <t>विनिमय</t>
-        </is>
-      </c>
-      <c r="B2271" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="C2271" t="inlineStr">
-        <is>
-          <t>vinimay</t>
-        </is>
-      </c>
-      <c r="F2271" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 20.</t>
-        </is>
-      </c>
-      <c r="I2271" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="2272">
-      <c r="A2272" t="inlineStr">
-        <is>
-          <t>विनिमय प्रणाली</t>
-        </is>
-      </c>
-      <c r="B2272" t="inlineStr">
-        <is>
-          <t>exchange system</t>
-        </is>
-      </c>
-      <c r="C2272" t="inlineStr">
-        <is>
-          <t>vinimay pranali</t>
-        </is>
-      </c>
-      <c r="F2272" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 20.</t>
-        </is>
-      </c>
-      <c r="I2272" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 51</t>
-        </is>
-      </c>
-    </row>
-    <row r="2273">
-      <c r="A2273" t="inlineStr">
-        <is>
-          <t>वस्तु विनिमय प्रणाली</t>
-        </is>
-      </c>
-      <c r="B2273" t="inlineStr">
-        <is>
-          <t>barter system</t>
-        </is>
-      </c>
-      <c r="C2273" t="inlineStr">
-        <is>
-          <t>vastu vinimay pranali</t>
-        </is>
-      </c>
-      <c r="F2273" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 20.</t>
-        </is>
-      </c>
-      <c r="I2273" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="2274">
-      <c r="A2274" t="inlineStr">
-        <is>
-          <t>श्रम विनिमय प्रणाली</t>
-        </is>
-      </c>
-      <c r="B2274" t="inlineStr">
-        <is>
-          <t>system of exchange of labour</t>
-        </is>
-      </c>
-      <c r="C2274" t="inlineStr">
-        <is>
-          <t>shram vinimay pranali</t>
-        </is>
-      </c>
-      <c r="F2274" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 20.</t>
-        </is>
-      </c>
-      <c r="I2274" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 62</t>
-        </is>
-      </c>
-    </row>
-    <row r="2275">
-      <c r="A2275" t="inlineStr">
-        <is>
-          <t>संग्रहण</t>
-        </is>
-      </c>
-      <c r="B2275" t="inlineStr">
-        <is>
-          <t>accumulating</t>
-        </is>
-      </c>
-      <c r="C2275" t="inlineStr">
-        <is>
-          <t>sangrahan</t>
-        </is>
-      </c>
-      <c r="F2275" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 21.</t>
-        </is>
-      </c>
-      <c r="I2275" t="inlineStr">
+      <c r="I2302" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 45</t>
+        </is>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" t="inlineStr">
+        <is>
+          <t>धातु कोष</t>
+        </is>
+      </c>
+      <c r="B2303" t="inlineStr">
+        <is>
+          <t>metal reserve</t>
+        </is>
+      </c>
+      <c r="C2303" t="inlineStr">
+        <is>
+          <t>dhatu kosh</t>
+        </is>
+      </c>
+      <c r="F2303" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 17.</t>
+        </is>
+      </c>
+      <c r="I2303" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 6</t>
         </is>
       </c>
     </row>
-    <row r="2276">
-      <c r="A2276" t="inlineStr">
-        <is>
-          <t>संग्रहवादी</t>
-        </is>
-      </c>
-      <c r="B2276" t="inlineStr">
-        <is>
-          <t>accumulation-oriented</t>
-        </is>
-      </c>
-      <c r="C2276" t="inlineStr">
-        <is>
-          <t>sangrahvadi</t>
-        </is>
-      </c>
-      <c r="F2276" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 21.</t>
-        </is>
-      </c>
-      <c r="I2276" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 46</t>
-        </is>
-      </c>
-    </row>
-    <row r="2277">
-      <c r="A2277" t="inlineStr">
-        <is>
-          <t>भोगवादी</t>
-        </is>
-      </c>
-      <c r="B2277" t="inlineStr">
-        <is>
-          <t>indulgence-oriented</t>
-        </is>
-      </c>
-      <c r="C2277" t="inlineStr">
-        <is>
-          <t>bhogvadi</t>
-        </is>
-      </c>
-      <c r="F2277" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 22.</t>
-        </is>
-      </c>
-      <c r="I2277" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 46</t>
-        </is>
-      </c>
-    </row>
-    <row r="2278">
-      <c r="A2278" t="inlineStr">
-        <is>
-          <t>उपभोक्तावादी</t>
-        </is>
-      </c>
-      <c r="B2278" t="inlineStr">
-        <is>
-          <t>consumerist</t>
-        </is>
-      </c>
-      <c r="C2278" t="inlineStr">
-        <is>
-          <t>upbhoktavadi</t>
-        </is>
-      </c>
-      <c r="F2278" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 22.</t>
-        </is>
-      </c>
-      <c r="I2278" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="2279">
-      <c r="A2279" t="inlineStr">
-        <is>
-          <t>विलासिता</t>
-        </is>
-      </c>
-      <c r="B2279" t="inlineStr">
-        <is>
-          <t>luxury</t>
-        </is>
-      </c>
-      <c r="C2279" t="inlineStr">
-        <is>
-          <t>vilasita</t>
-        </is>
-      </c>
-      <c r="F2279" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 22.</t>
-        </is>
-      </c>
-      <c r="I2279" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="2280">
-      <c r="A2280" t="inlineStr">
-        <is>
-          <t>सुविधा संग्रह</t>
-        </is>
-      </c>
-      <c r="B2280" t="inlineStr">
-        <is>
-          <t>accumulation of comforts</t>
-        </is>
-      </c>
-      <c r="C2280" t="inlineStr">
-        <is>
-          <t>suvidha sangrah</t>
-        </is>
-      </c>
-      <c r="F2280" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 23.</t>
-        </is>
-      </c>
-      <c r="I2280" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 83</t>
-        </is>
-      </c>
-    </row>
-    <row r="2281">
-      <c r="A2281" t="inlineStr">
-        <is>
-          <t>सुविधावादी मानसिकता</t>
-        </is>
-      </c>
-      <c r="B2281" t="inlineStr">
-        <is>
-          <t>comfort-oriented mentality</t>
-        </is>
-      </c>
-      <c r="C2281" t="inlineStr">
-        <is>
-          <t>suvidhavadi mansikta</t>
-        </is>
-      </c>
-      <c r="F2281" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 23.</t>
-        </is>
-      </c>
-      <c r="I2281" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 75</t>
-        </is>
-      </c>
-    </row>
-    <row r="2282">
-      <c r="A2282" t="inlineStr">
-        <is>
-          <t>दोहन</t>
-        </is>
-      </c>
-      <c r="B2282" t="inlineStr">
-        <is>
-          <t>extraction</t>
-        </is>
-      </c>
-      <c r="C2282" t="inlineStr">
-        <is>
-          <t>dohan</t>
-        </is>
-      </c>
-      <c r="F2282" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 24.</t>
-        </is>
-      </c>
-      <c r="I2282" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 68</t>
-        </is>
-      </c>
-    </row>
-    <row r="2283">
-      <c r="A2283" t="inlineStr">
-        <is>
-          <t>राजगद्दी के कर विधि</t>
-        </is>
-      </c>
-      <c r="B2283" t="inlineStr">
-        <is>
-          <t>taxation by the throne</t>
-        </is>
-      </c>
-      <c r="C2283" t="inlineStr">
-        <is>
-          <t>rajgaddi ke kar vidhi</t>
-        </is>
-      </c>
-      <c r="F2283" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 25.</t>
-        </is>
-      </c>
-      <c r="I2283" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="2284">
-      <c r="A2284" t="inlineStr">
-        <is>
-          <t>कर वसूली</t>
-        </is>
-      </c>
-      <c r="B2284" t="inlineStr">
-        <is>
-          <t>tax collection</t>
-        </is>
-      </c>
-      <c r="C2284" t="inlineStr">
-        <is>
-          <t>kar vasuli</t>
-        </is>
-      </c>
-      <c r="F2284" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 25.</t>
-        </is>
-      </c>
-      <c r="I2284" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 138</t>
-        </is>
-      </c>
-    </row>
-    <row r="2285">
-      <c r="A2285" t="inlineStr">
-        <is>
-          <t>स्वायत्त</t>
-        </is>
-      </c>
-      <c r="B2285" t="inlineStr">
-        <is>
-          <t>autonomous</t>
-        </is>
-      </c>
-      <c r="C2285" t="inlineStr">
-        <is>
-          <t>swayatt</t>
-        </is>
-      </c>
-      <c r="F2285" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 26.</t>
-        </is>
-      </c>
-      <c r="I2285" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 26</t>
-        </is>
-      </c>
-    </row>
-    <row r="2286">
-      <c r="A2286" t="inlineStr">
-        <is>
-          <t>स्वावलंबी</t>
-        </is>
-      </c>
-      <c r="B2286" t="inlineStr">
-        <is>
-          <t>self-reliant</t>
-        </is>
-      </c>
-      <c r="C2286" t="inlineStr">
-        <is>
-          <t>swavalambi</t>
-        </is>
-      </c>
-      <c r="F2286" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 26.</t>
-        </is>
-      </c>
-      <c r="I2286" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 26</t>
-        </is>
-      </c>
-    </row>
-    <row r="2287">
-      <c r="A2287" t="inlineStr">
-        <is>
-          <t>परिवार मूलक ग्राम स्वराज्य व्यवस्था</t>
-        </is>
-      </c>
-      <c r="B2287" t="inlineStr">
-        <is>
-          <t>family-based village self-governing system</t>
-        </is>
-      </c>
-      <c r="C2287" t="inlineStr">
-        <is>
-          <t>parivar mulak gram swarajya vyavastha</t>
-        </is>
-      </c>
-      <c r="F2287" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 27.</t>
-        </is>
-      </c>
-      <c r="I2287" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 110</t>
-        </is>
-      </c>
-    </row>
-    <row r="2288">
-      <c r="A2288" t="inlineStr">
-        <is>
-          <t>आबंटन</t>
-        </is>
-      </c>
-      <c r="B2288" t="inlineStr">
-        <is>
-          <t>allotment</t>
-        </is>
-      </c>
-      <c r="C2288" t="inlineStr">
-        <is>
-          <t>abantan</t>
-        </is>
-      </c>
-      <c r="F2288" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 29.</t>
-        </is>
-      </c>
-      <c r="I2288" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2289">
-      <c r="A2289" t="inlineStr">
-        <is>
-          <t>बंटन</t>
-        </is>
-      </c>
-      <c r="B2289" t="inlineStr">
-        <is>
-          <t>sharing</t>
-        </is>
-      </c>
-      <c r="C2289" t="inlineStr">
-        <is>
-          <t>bantan</t>
-        </is>
-      </c>
-      <c r="F2289" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 29.</t>
-        </is>
-      </c>
-      <c r="I2289" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2290">
-      <c r="A2290" t="inlineStr">
-        <is>
-          <t>वितरण</t>
-        </is>
-      </c>
-      <c r="B2290" t="inlineStr">
-        <is>
-          <t>distribution</t>
-        </is>
-      </c>
-      <c r="C2290" t="inlineStr">
-        <is>
-          <t>vitaran</t>
-        </is>
-      </c>
-      <c r="F2290" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 29.</t>
-        </is>
-      </c>
-      <c r="I2290" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 26</t>
-        </is>
-      </c>
-    </row>
-    <row r="2291">
-      <c r="A2291" t="inlineStr">
-        <is>
-          <t>कुटीर उद्योग</t>
-        </is>
-      </c>
-      <c r="B2291" t="inlineStr">
-        <is>
-          <t>cottage industry</t>
-        </is>
-      </c>
-      <c r="C2291" t="inlineStr">
-        <is>
-          <t>kutir udyog</t>
-        </is>
-      </c>
-      <c r="F2291" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 30.</t>
-        </is>
-      </c>
-      <c r="I2291" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 71</t>
-        </is>
-      </c>
-    </row>
-    <row r="2292">
-      <c r="A2292" t="inlineStr">
-        <is>
-          <t>ग्राम शिल्प</t>
-        </is>
-      </c>
-      <c r="B2292" t="inlineStr">
-        <is>
-          <t>village crafts</t>
-        </is>
-      </c>
-      <c r="C2292" t="inlineStr">
-        <is>
-          <t>gram shilp</t>
-        </is>
-      </c>
-      <c r="F2292" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 30.</t>
-        </is>
-      </c>
-      <c r="I2292" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 71</t>
-        </is>
-      </c>
-    </row>
-    <row r="2293">
-      <c r="A2293" t="inlineStr">
-        <is>
-          <t>ग्रामोद्योग</t>
-        </is>
-      </c>
-      <c r="B2293" t="inlineStr">
-        <is>
-          <t>village industry</t>
-        </is>
-      </c>
-      <c r="C2293" t="inlineStr">
-        <is>
-          <t>gramodyog</t>
-        </is>
-      </c>
-      <c r="F2293" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 30.</t>
-        </is>
-      </c>
-      <c r="I2293" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 27</t>
-        </is>
-      </c>
-    </row>
-    <row r="2294">
-      <c r="A2294" t="inlineStr">
-        <is>
-          <t>कृषि</t>
-        </is>
-      </c>
-      <c r="B2294" t="inlineStr">
-        <is>
-          <t>agriculture</t>
-        </is>
-      </c>
-      <c r="C2294" t="inlineStr">
-        <is>
-          <t>krishi</t>
-        </is>
-      </c>
-      <c r="F2294" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 30.</t>
-        </is>
-      </c>
-      <c r="I2294" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 71</t>
-        </is>
-      </c>
-    </row>
-    <row r="2295">
-      <c r="A2295" t="inlineStr">
-        <is>
-          <t>गोपालन</t>
-        </is>
-      </c>
-      <c r="B2295" t="inlineStr">
-        <is>
-          <t>cattle-rearing</t>
-        </is>
-      </c>
-      <c r="C2295" t="inlineStr">
-        <is>
-          <t>gopalan</t>
-        </is>
-      </c>
-      <c r="F2295" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 30.</t>
-        </is>
-      </c>
-      <c r="I2295" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 71</t>
-        </is>
-      </c>
-    </row>
-    <row r="2296">
-      <c r="A2296" t="inlineStr">
-        <is>
-          <t>ठोस</t>
-        </is>
-      </c>
-      <c r="B2296" t="inlineStr">
-        <is>
-          <t>solid</t>
-        </is>
-      </c>
-      <c r="C2296" t="inlineStr">
-        <is>
-          <t>thos</t>
-        </is>
-      </c>
-      <c r="F2296" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 35.</t>
-        </is>
-      </c>
-      <c r="I2296" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 34</t>
-        </is>
-      </c>
-    </row>
-    <row r="2297">
-      <c r="A2297" t="inlineStr">
-        <is>
-          <t>तरल</t>
-        </is>
-      </c>
-      <c r="B2297" t="inlineStr">
-        <is>
-          <t>liquid</t>
-        </is>
-      </c>
-      <c r="C2297" t="inlineStr">
-        <is>
-          <t>taral</t>
-        </is>
-      </c>
-      <c r="F2297" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 35.</t>
-        </is>
-      </c>
-      <c r="I2297" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 34</t>
-        </is>
-      </c>
-    </row>
-    <row r="2298">
-      <c r="A2298" t="inlineStr">
-        <is>
-          <t>विरल वस्तु</t>
-        </is>
-      </c>
-      <c r="B2298" t="inlineStr">
-        <is>
-          <t>rarefied (gaseous) matter</t>
-        </is>
-      </c>
-      <c r="C2298" t="inlineStr">
-        <is>
-          <t>viral vastu</t>
-        </is>
-      </c>
-      <c r="F2298" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 35.</t>
-        </is>
-      </c>
-      <c r="I2298" t="inlineStr">
-        <is>
-          <t>AA-Glossary-Additions.md; AA p. 34</t>
+    <row r="2304">
+      <c r="A2304" t="inlineStr">
+        <is>
+          <t>धातु कोषालय</t>
+        </is>
+      </c>
+      <c r="B2304" t="inlineStr">
+        <is>
+          <t>metal treasury</t>
+        </is>
+      </c>
+      <c r="C2304" t="inlineStr">
+        <is>
+          <t>dhatu koshalay</t>
+        </is>
+      </c>
+      <c r="F2304" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 17.</t>
+        </is>
+      </c>
+      <c r="I2304" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 6</t>
         </is>
       </c>
     </row>

--- a/References/Madhyasth-Darshan/MD-Mapping.xlsx
+++ b/References/Madhyasth-Darshan/MD-Mapping.xlsx
@@ -911,7 +911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2304"/>
+  <dimension ref="A1:K2305"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.4399995803833" defaultRowHeight="15"/>
   <cols>
     <col width="23.21999931335449" customWidth="1" style="114" min="1" max="1"/>
@@ -62256,164 +62256,191 @@
       </c>
     </row>
     <row r="2299">
-      <c r="A2299" t="inlineStr">
+      <c r="A2299" s="0" t="inlineStr">
         <is>
           <t>राष्ट्रीय मुद्रा कोष, राष्ट्रीय मुद्राकोष</t>
         </is>
       </c>
-      <c r="B2299" t="inlineStr">
+      <c r="B2299" s="0" t="inlineStr">
         <is>
           <t>reserve bank</t>
         </is>
       </c>
-      <c r="C2299" t="inlineStr">
+      <c r="C2299" s="0" t="inlineStr">
         <is>
           <t>rashtriya mudra kosh</t>
         </is>
       </c>
-      <c r="F2299" t="inlineStr">
+      <c r="F2299" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 17.</t>
         </is>
       </c>
-      <c r="I2299" t="inlineStr">
+      <c r="I2299" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA pp. 44-45</t>
         </is>
       </c>
     </row>
     <row r="2300">
-      <c r="A2300" t="inlineStr">
+      <c r="A2300" s="0" t="inlineStr">
         <is>
           <t>अंतर्राष्ट्रीय मुद्रा कोष</t>
         </is>
       </c>
-      <c r="B2300" t="inlineStr">
+      <c r="B2300" s="0" t="inlineStr">
         <is>
           <t>International Monetary Fund</t>
         </is>
       </c>
-      <c r="C2300" t="inlineStr">
+      <c r="C2300" s="0" t="inlineStr">
         <is>
           <t>antarrashtriya mudra kosh</t>
         </is>
       </c>
-      <c r="F2300" t="inlineStr">
+      <c r="F2300" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 17.</t>
         </is>
       </c>
-      <c r="I2300" t="inlineStr">
+      <c r="I2300" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 44</t>
         </is>
       </c>
     </row>
     <row r="2301">
-      <c r="A2301" t="inlineStr">
+      <c r="A2301" s="0" t="inlineStr">
         <is>
           <t>अन्तर्राष्ट्रीय कोष, अंतर्राष्ट्रीय कोष</t>
         </is>
       </c>
-      <c r="B2301" t="inlineStr">
+      <c r="B2301" s="0" t="inlineStr">
         <is>
           <t>international reserves</t>
         </is>
       </c>
-      <c r="C2301" t="inlineStr">
+      <c r="C2301" s="0" t="inlineStr">
         <is>
           <t>antarrashtriya kosh</t>
         </is>
       </c>
-      <c r="F2301" t="inlineStr">
+      <c r="F2301" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 17.</t>
         </is>
       </c>
-      <c r="I2301" t="inlineStr">
+      <c r="I2301" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 51</t>
         </is>
       </c>
     </row>
     <row r="2302">
-      <c r="A2302" t="inlineStr">
+      <c r="A2302" s="0" t="inlineStr">
         <is>
           <t>मुद्रा कोष</t>
         </is>
       </c>
-      <c r="B2302" t="inlineStr">
+      <c r="B2302" s="0" t="inlineStr">
         <is>
           <t>currency reserve</t>
         </is>
       </c>
-      <c r="C2302" t="inlineStr">
+      <c r="C2302" s="0" t="inlineStr">
         <is>
           <t>mudra kosh</t>
         </is>
       </c>
-      <c r="F2302" t="inlineStr">
+      <c r="F2302" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 17.</t>
         </is>
       </c>
-      <c r="I2302" t="inlineStr">
+      <c r="I2302" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 45</t>
         </is>
       </c>
     </row>
     <row r="2303">
-      <c r="A2303" t="inlineStr">
+      <c r="A2303" s="0" t="inlineStr">
         <is>
           <t>धातु कोष</t>
         </is>
       </c>
-      <c r="B2303" t="inlineStr">
+      <c r="B2303" s="0" t="inlineStr">
         <is>
           <t>metal reserve</t>
         </is>
       </c>
-      <c r="C2303" t="inlineStr">
+      <c r="C2303" s="0" t="inlineStr">
         <is>
           <t>dhatu kosh</t>
         </is>
       </c>
-      <c r="F2303" t="inlineStr">
+      <c r="F2303" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 17.</t>
         </is>
       </c>
-      <c r="I2303" t="inlineStr">
+      <c r="I2303" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 6</t>
         </is>
       </c>
     </row>
     <row r="2304">
-      <c r="A2304" t="inlineStr">
+      <c r="A2304" s="0" t="inlineStr">
         <is>
           <t>धातु कोषालय</t>
         </is>
       </c>
-      <c r="B2304" t="inlineStr">
+      <c r="B2304" s="0" t="inlineStr">
         <is>
           <t>metal treasury</t>
         </is>
       </c>
-      <c r="C2304" t="inlineStr">
+      <c r="C2304" s="0" t="inlineStr">
         <is>
           <t>dhatu koshalay</t>
         </is>
       </c>
-      <c r="F2304" t="inlineStr">
+      <c r="F2304" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 17.</t>
         </is>
       </c>
-      <c r="I2304" t="inlineStr">
+      <c r="I2304" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="2305">
+      <c r="A2305" t="inlineStr">
+        <is>
+          <t>नियतिक्रम</t>
+        </is>
+      </c>
+      <c r="B2305" t="inlineStr">
+        <is>
+          <t>natural progression</t>
+        </is>
+      </c>
+      <c r="C2305" t="inlineStr">
+        <is>
+          <t>niyatikram</t>
+        </is>
+      </c>
+      <c r="F2305" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026), following KD's front matter. MVD p. 8 and SB render the same passage 'destiny progression'; MVD uses 'natural progression' for अनुक्रम.</t>
+        </is>
+      </c>
+      <c r="I2305" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA PDF p. 6; KD front matter</t>
         </is>
       </c>
     </row>

--- a/References/Madhyasth-Darshan/MD-Mapping.xlsx
+++ b/References/Madhyasth-Darshan/MD-Mapping.xlsx
@@ -911,7 +911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2305"/>
+  <dimension ref="A1:K2309"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.4399995803833" defaultRowHeight="15"/>
   <cols>
     <col width="23.21999931335449" customWidth="1" style="114" min="1" max="1"/>
@@ -8757,6 +8757,11 @@
       </c>
       <c r="D238" s="118" t="n"/>
       <c r="E238" s="119" t="n"/>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Confirmed as 'independence' (project-wide decision of the author, 13 October 2026); the AA chapter 7 title is 'Awakening and Independence'. कर्म स्वतंत्रता stays 'freedom of action'.</t>
+        </is>
+      </c>
       <c r="G238" s="120" t="inlineStr">
         <is>
           <t>ownership, identity</t>
@@ -28804,7 +28809,7 @@
       </c>
       <c r="F870" s="121" t="inlineStr">
         <is>
-          <t>in some contexts 'suvidha' has been used for indicating 'luxury'.</t>
+          <t>in some contexts 'suvidha' has been used for indicating 'luxury'. | 'facilities' where सुविधा means public or village services (project-wide decision of the author, 13 October 2026; see the row 'सुविधा (public services)').</t>
         </is>
       </c>
       <c r="G870" s="121" t="inlineStr">
@@ -34777,7 +34782,7 @@
       <c r="E1061" s="119" t="n"/>
       <c r="F1061" s="120" t="inlineStr">
         <is>
-          <t>tva sahit vyavastha, samagra vyavastha me bhagidari</t>
+          <t>tva sahit vyavastha, samagra vyavastha me bhagidari | Confirmed as 'independence' (project-wide decision of the author, 13 October 2026); the AA chapter 7 title is 'Awakening and Independence'. कर्म स्वतंत्रता stays 'freedom of action'.</t>
         </is>
       </c>
       <c r="G1061" s="121" t="n"/>
@@ -43557,7 +43562,7 @@
       </c>
       <c r="B1337" s="116" t="inlineStr">
         <is>
-          <t>doing</t>
+          <t>done</t>
         </is>
       </c>
       <c r="C1337" s="117" t="inlineStr">
@@ -43571,7 +43576,11 @@
         </is>
       </c>
       <c r="E1337" s="119" t="n"/>
-      <c r="F1337" s="120" t="n"/>
+      <c r="F1337" s="120" t="inlineStr">
+        <is>
+          <t>In the triad कृत, कारित, अनुमोदित: done, caused, intended (project-wide decision of the author, 13 October 2026; the author's KD rendering, settled 8 July 2026). Formerly 'doing'.</t>
+        </is>
+      </c>
       <c r="G1337" s="121" t="n"/>
       <c r="H1337" s="121" t="n"/>
       <c r="I1337" s="120" t="inlineStr">
@@ -43590,7 +43599,7 @@
       </c>
       <c r="B1338" s="116" t="inlineStr">
         <is>
-          <t>getting done</t>
+          <t>caused</t>
         </is>
       </c>
       <c r="C1338" s="117" t="inlineStr">
@@ -43606,7 +43615,7 @@
       <c r="E1338" s="119" t="n"/>
       <c r="F1338" s="120" t="inlineStr">
         <is>
-          <t>delegating</t>
+          <t>delegating | In the triad कृत, कारित, अनुमोदित: done, caused, intended (project-wide decision of the author, 13 October 2026; the author's KD rendering, settled 8 July 2026). Formerly 'getting done'.</t>
         </is>
       </c>
       <c r="G1338" s="121" t="n"/>
@@ -43627,7 +43636,7 @@
       </c>
       <c r="B1339" s="116" t="inlineStr">
         <is>
-          <t>consenting</t>
+          <t>intended</t>
         </is>
       </c>
       <c r="C1339" s="117" t="inlineStr">
@@ -43643,7 +43652,7 @@
       <c r="E1339" s="119" t="n"/>
       <c r="F1339" s="120" t="inlineStr">
         <is>
-          <t>consenting, approving, subscribing</t>
+          <t>consenting, approving, subscribing | In the triad कृत, कारित, अनुमोदित: done, caused, intended (project-wide decision of the author, 13 October 2026; the author's KD rendering, settled 8 July 2026). Formerly 'consenting'.</t>
         </is>
       </c>
       <c r="G1339" s="121" t="n"/>
@@ -62418,29 +62427,137 @@
       </c>
     </row>
     <row r="2305">
-      <c r="A2305" t="inlineStr">
+      <c r="A2305" s="0" t="inlineStr">
         <is>
           <t>नियतिक्रम</t>
         </is>
       </c>
-      <c r="B2305" t="inlineStr">
+      <c r="B2305" s="0" t="inlineStr">
         <is>
           <t>natural progression</t>
         </is>
       </c>
-      <c r="C2305" t="inlineStr">
+      <c r="C2305" s="0" t="inlineStr">
         <is>
           <t>niyatikram</t>
         </is>
       </c>
-      <c r="F2305" t="inlineStr">
+      <c r="F2305" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of 7 October 2026), following KD's front matter. MVD p. 8 and SB render the same passage 'destiny progression'; MVD uses 'natural progression' for अनुक्रम.</t>
         </is>
       </c>
-      <c r="I2305" t="inlineStr">
+      <c r="I2305" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA PDF p. 6; KD front matter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2306">
+      <c r="A2306" t="inlineStr">
+        <is>
+          <t>अस्तित्व दर्शन ज्ञान</t>
+        </is>
+      </c>
+      <c r="B2306" t="inlineStr">
+        <is>
+          <t>knowledge of coexistence</t>
+        </is>
+      </c>
+      <c r="C2306" t="inlineStr">
+        <is>
+          <t>astitva darshan gyan</t>
+        </is>
+      </c>
+      <c r="F2306" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of the author, 13 October 2026), following the author's wording on AA p. 12. Supersedes MVD's 'knowledge of the holistic view of existence' (MVD p. 259) for this compound; bare अस्तित्व दर्शन and सह-अस्तित्व दर्शन ज्ञान are unchanged.</t>
+        </is>
+      </c>
+      <c r="I2306" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA pp. 12, 19, 47, 99, 102, 113, 121; KD pp. 30, 69</t>
+        </is>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" t="inlineStr">
+        <is>
+          <t>कृत, कारित, अनुमोदित</t>
+        </is>
+      </c>
+      <c r="B2307" t="inlineStr">
+        <is>
+          <t>done, caused, intended</t>
+        </is>
+      </c>
+      <c r="C2307" t="inlineStr">
+        <is>
+          <t>krit, karit, anumodit</t>
+        </is>
+      </c>
+      <c r="F2307" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of the author, 13 October 2026): the author's KD rendering (settled 8 July 2026) made project-wide; MVD p. 244 has doing, getting done, consenting.</t>
+        </is>
+      </c>
+      <c r="I2307" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA pp. 60, 99; KD-Glossary-Additions.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="A2308" t="inlineStr">
+        <is>
+          <t>संतुष्टि</t>
+        </is>
+      </c>
+      <c r="B2308" t="inlineStr">
+        <is>
+          <t>contentment</t>
+        </is>
+      </c>
+      <c r="C2308" t="inlineStr">
+        <is>
+          <t>santushti</t>
+        </is>
+      </c>
+      <c r="F2308" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of the author, 13 October 2026). Shares 'contentment' with संतोष (the jeevan value); where the distinction matters, the Hindi word is the guide.</t>
+        </is>
+      </c>
+      <c r="I2308" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 48</t>
+        </is>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="A2309" t="inlineStr">
+        <is>
+          <t>सुविधा (public services)</t>
+        </is>
+      </c>
+      <c r="B2309" t="inlineStr">
+        <is>
+          <t>facilities</t>
+        </is>
+      </c>
+      <c r="C2309" t="inlineStr">
+        <is>
+          <t>suvidha</t>
+        </is>
+      </c>
+      <c r="F2309" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of the author, 13 October 2026): सुविधा in the sense of village or public services (drinking water, school, roads, post office, bank). Elsewhere सुविधा = comfort(s).</t>
+        </is>
+      </c>
+      <c r="I2309" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA chapter 9</t>
         </is>
       </c>
     </row>

--- a/References/Madhyasth-Darshan/MD-Mapping.xlsx
+++ b/References/Madhyasth-Darshan/MD-Mapping.xlsx
@@ -911,7 +911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2309"/>
+  <dimension ref="A1:K2310"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.4399995803833" defaultRowHeight="15"/>
   <cols>
     <col width="23.21999931335449" customWidth="1" style="114" min="1" max="1"/>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="D238" s="118" t="n"/>
       <c r="E238" s="119" t="n"/>
-      <c r="F238" t="inlineStr">
+      <c r="F238" s="0" t="inlineStr">
         <is>
           <t>Confirmed as 'independence' (project-wide decision of the author, 13 October 2026); the AA chapter 7 title is 'Awakening and Independence'. कर्म स्वतंत्रता stays 'freedom of action'.</t>
         </is>
@@ -62454,110 +62454,137 @@
       </c>
     </row>
     <row r="2306">
-      <c r="A2306" t="inlineStr">
+      <c r="A2306" s="0" t="inlineStr">
         <is>
           <t>अस्तित्व दर्शन ज्ञान</t>
         </is>
       </c>
-      <c r="B2306" t="inlineStr">
+      <c r="B2306" s="0" t="inlineStr">
         <is>
           <t>knowledge of coexistence</t>
         </is>
       </c>
-      <c r="C2306" t="inlineStr">
+      <c r="C2306" s="0" t="inlineStr">
         <is>
           <t>astitva darshan gyan</t>
         </is>
       </c>
-      <c r="F2306" t="inlineStr">
-        <is>
-          <t>AA glossary addition (project-wide decision of the author, 13 October 2026), following the author's wording on AA p. 12. Supersedes MVD's 'knowledge of the holistic view of existence' (MVD p. 259) for this compound; bare अस्तित्व दर्शन and सह-अस्तित्व दर्शन ज्ञान are unchanged.</t>
-        </is>
-      </c>
-      <c r="I2306" t="inlineStr">
+      <c r="F2306" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of the author, 13 October 2026), following the author's wording on AA p. 12. Supersedes MVD's 'knowledge of the holistic view of existence' (MVD p. 259) for this compound; bare अस्तित्व दर्शन = holistic view of existence (row 2310); सह-अस्तित्व दर्शन ज्ञान is unchanged.</t>
+        </is>
+      </c>
+      <c r="I2306" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA pp. 12, 19, 47, 99, 102, 113, 121; KD pp. 30, 69</t>
         </is>
       </c>
     </row>
     <row r="2307">
-      <c r="A2307" t="inlineStr">
+      <c r="A2307" s="0" t="inlineStr">
         <is>
           <t>कृत, कारित, अनुमोदित</t>
         </is>
       </c>
-      <c r="B2307" t="inlineStr">
+      <c r="B2307" s="0" t="inlineStr">
         <is>
           <t>done, caused, intended</t>
         </is>
       </c>
-      <c r="C2307" t="inlineStr">
+      <c r="C2307" s="0" t="inlineStr">
         <is>
           <t>krit, karit, anumodit</t>
         </is>
       </c>
-      <c r="F2307" t="inlineStr">
+      <c r="F2307" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of the author, 13 October 2026): the author's KD rendering (settled 8 July 2026) made project-wide; MVD p. 244 has doing, getting done, consenting.</t>
         </is>
       </c>
-      <c r="I2307" t="inlineStr">
+      <c r="I2307" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA pp. 60, 99; KD-Glossary-Additions.md</t>
         </is>
       </c>
     </row>
     <row r="2308">
-      <c r="A2308" t="inlineStr">
+      <c r="A2308" s="0" t="inlineStr">
         <is>
           <t>संतुष्टि</t>
         </is>
       </c>
-      <c r="B2308" t="inlineStr">
+      <c r="B2308" s="0" t="inlineStr">
         <is>
           <t>contentment</t>
         </is>
       </c>
-      <c r="C2308" t="inlineStr">
+      <c r="C2308" s="0" t="inlineStr">
         <is>
           <t>santushti</t>
         </is>
       </c>
-      <c r="F2308" t="inlineStr">
+      <c r="F2308" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of the author, 13 October 2026). Shares 'contentment' with संतोष (the jeevan value); where the distinction matters, the Hindi word is the guide.</t>
         </is>
       </c>
-      <c r="I2308" t="inlineStr">
+      <c r="I2308" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 48</t>
         </is>
       </c>
     </row>
     <row r="2309">
-      <c r="A2309" t="inlineStr">
+      <c r="A2309" s="0" t="inlineStr">
         <is>
           <t>सुविधा (public services)</t>
         </is>
       </c>
-      <c r="B2309" t="inlineStr">
+      <c r="B2309" s="0" t="inlineStr">
         <is>
           <t>facilities</t>
         </is>
       </c>
-      <c r="C2309" t="inlineStr">
+      <c r="C2309" s="0" t="inlineStr">
         <is>
           <t>suvidha</t>
         </is>
       </c>
-      <c r="F2309" t="inlineStr">
+      <c r="F2309" s="0" t="inlineStr">
         <is>
           <t>AA glossary addition (project-wide decision of the author, 13 October 2026): सुविधा in the sense of village or public services (drinking water, school, roads, post office, bank). Elsewhere सुविधा = comfort(s).</t>
         </is>
       </c>
-      <c r="I2309" t="inlineStr">
+      <c r="I2309" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA chapter 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="2310">
+      <c r="A2310" s="0" t="inlineStr">
+        <is>
+          <t>अस्तित्व दर्शन</t>
+        </is>
+      </c>
+      <c r="B2310" s="0" t="inlineStr">
+        <is>
+          <t>holistic view of existence</t>
+        </is>
+      </c>
+      <c r="C2310" s="0" t="inlineStr">
+        <is>
+          <t>astitva darshan</t>
+        </is>
+      </c>
+      <c r="F2310" s="0" t="inlineStr">
+        <is>
+          <t>Decision of the author, 13 October 2026, for bare अस्तित्व दर्शन (without ज्ञान): follows KD (दर्शन = the holistic view of X, settled 8 July 2026), row 566 (दर्शन = holistic view) and MVD p. 259. Replaces AA's earlier 'the darshan of existence'. With ज्ञान, see row 2306.</t>
+        </is>
+      </c>
+      <c r="I2310" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA pp. 14, 15, 23, 38, 47, 65, 66, 76, 82, 85, 94, 95, 99, 108, 115; KD-Glossary-Additions.md</t>
         </is>
       </c>
     </row>

--- a/References/Madhyasth-Darshan/MD-Mapping.xlsx
+++ b/References/Madhyasth-Darshan/MD-Mapping.xlsx
@@ -911,7 +911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2310"/>
+  <dimension ref="A1:K2311"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.4399995803833" defaultRowHeight="15"/>
   <cols>
     <col width="23.21999931335449" customWidth="1" style="114" min="1" max="1"/>
@@ -21802,7 +21802,7 @@
       </c>
       <c r="B650" s="28" t="inlineStr">
         <is>
-          <t>societal participation</t>
+          <t>social participation</t>
         </is>
       </c>
       <c r="C650" s="117" t="inlineStr">
@@ -21818,12 +21818,16 @@
       </c>
       <c r="F650" s="120" t="inlineStr">
         <is>
-          <t>societal functioning</t>
+          <t>societal functioning; [Updated "societal participation" -&gt; "social participation" per author decision, 2026-10-16, aligning with JV p. 154.]</t>
         </is>
       </c>
       <c r="G650" s="121" t="n"/>
       <c r="H650" s="121" t="n"/>
-      <c r="I650" s="121" t="n"/>
+      <c r="I650" s="121" t="inlineStr">
+        <is>
+          <t>JV p. 154; AA pp. 72, 94, 114, 116; KD pp. 115-116</t>
+        </is>
+      </c>
       <c r="J650" s="40" t="n"/>
       <c r="K650" s="40" t="n"/>
     </row>
@@ -62585,6 +62589,33 @@
       <c r="I2310" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA pp. 14, 15, 23, 38, 47, 65, 66, 76, 82, 85, 94, 95, 99, 108, 115; KD-Glossary-Additions.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="2311">
+      <c r="A2311" t="inlineStr">
+        <is>
+          <t>समझदार परिवार</t>
+        </is>
+      </c>
+      <c r="B2311" t="inlineStr">
+        <is>
+          <t>wise family</t>
+        </is>
+      </c>
+      <c r="C2311" t="inlineStr">
+        <is>
+          <t>samajhdar parivar</t>
+        </is>
+      </c>
+      <c r="F2311" t="inlineStr">
+        <is>
+          <t>Project-wide decision of the author, 16 October 2026: wise family for समझदार परिवार, replacing earlier "understanding family" / "understanding-endowed family".</t>
+        </is>
+      </c>
+      <c r="I2311" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA pp. 27, 120; KD-Glossary-Additions.md; KD p. 115</t>
         </is>
       </c>
     </row>
